--- a/assets/work-product-templates/comps/Lease Comps Template - Briggs.xlsx
+++ b/assets/work-product-templates/comps/Lease Comps Template - Briggs.xlsx
@@ -35,42 +35,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Trebuchet MS"/>
+      <name val="Calibri Light"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Trebuchet MS"/>
+      <name val="Calibri Light"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="Trebuchet MS"/>
+      <name val="Calibri Light"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <color rgb="FF3D4A54"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF3D4A54"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF6A748C"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF191919"/>
       <sz val="11"/>
